--- a/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
@@ -548,22 +548,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="3.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="2" width="3.139196" customWidth="1"/>
     <x:col min="3" max="3" width="9.853482" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="12.567768" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
@@ -574,10 +571,10 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
@@ -588,10 +585,10 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
@@ -602,10 +599,10 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
@@ -616,10 +613,10 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0">
+      <x:c r="A5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
@@ -630,10 +627,10 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0">
+      <x:c r="A6">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
@@ -644,10 +641,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0">
+      <x:c r="A7">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
@@ -658,10 +655,10 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
-      <x:c r="A8" s="0">
+      <x:c r="A8">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="B8" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
@@ -672,10 +669,10 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0">
+      <x:c r="A9">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="B9" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
@@ -686,10 +683,10 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0">
+      <x:c r="A10">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="B10" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
@@ -700,10 +697,10 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0">
+      <x:c r="A11">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="B11" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
@@ -714,10 +711,10 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
-      <x:c r="A12" s="0">
+      <x:c r="A12">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="B12" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
@@ -728,10 +725,10 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
-      <x:c r="A13" s="0">
+      <x:c r="A13">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="B13" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
@@ -742,10 +739,10 @@
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
-      <x:c r="A14" s="0">
+      <x:c r="A14">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="B14" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
@@ -756,10 +753,10 @@
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
-      <x:c r="A15" s="0">
+      <x:c r="A15">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="B15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
@@ -770,10 +767,10 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
-      <x:c r="A16" s="0">
+      <x:c r="A16">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B16" s="0" t="s">
+      <x:c r="B16" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
@@ -784,10 +781,10 @@
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
-      <x:c r="A17" s="0">
+      <x:c r="A17">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="B17" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
@@ -798,10 +795,10 @@
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
-      <x:c r="A18" s="0">
+      <x:c r="A18">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="B18" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
@@ -812,10 +809,10 @@
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
-      <x:c r="A19" s="0">
+      <x:c r="A19">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
+      <x:c r="B19" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
@@ -826,10 +823,10 @@
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
-      <x:c r="A20" s="0">
+      <x:c r="A20">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="B20" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
@@ -840,10 +837,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
@@ -552,8 +552,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="3.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="9.853482" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="12.567768" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="11.996339" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">

--- a/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/StyleIncludeQuotePrefix.xlsx
@@ -551,9 +551,9 @@
   <x:dimension ref="A1:D20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="3.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="9.567768" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="11.996339" style="1" customWidth="1"/>
+    <x:col min="1" max="2" width="3.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="9.571429" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="12" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
